--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/Dausa_Survey_Analysis_Single_Sheet.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/Dausa_Survey_Analysis_Single_Sheet.xlsx
@@ -830,23 +830,23 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>2253000</v>
+        <v>1621000</v>
       </c>
       <c r="F9" s="8">
         <f>IF(D9&gt;0, E9/D9, 0)</f>
         <v/>
       </c>
       <c r="G9" s="9" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>175000</v>
+        <v>150000</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1139000</v>
+        <v>729000</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>0</v>
@@ -855,16 +855,16 @@
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>309000</v>
+        <v>252000</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>320000</v>
+        <v>280000</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>80000</v>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -962,23 +962,23 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>73000</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8">
         <f>IF(D11&gt;0, E11/D11, 0)</f>
         <v/>
       </c>
       <c r="G11" s="9" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="14" t="n">
         <v>1</v>
@@ -2871,7 +2871,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -2917,13 +2917,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">

--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/Dausa_Survey_Analysis_Single_Sheet.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/Dausa_Survey_Analysis_Single_Sheet.xlsx
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="U18" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
